--- a/output/pdf_financials_xlsx/LG.xlsx
+++ b/output/pdf_financials_xlsx/LG.xlsx
@@ -652,19 +652,19 @@
         <v>0.000969</v>
       </c>
       <c r="C10" s="3" t="n">
-        <v>0.006184</v>
+        <v>0.514823</v>
       </c>
       <c r="D10" s="3" t="n">
-        <v>0.087992</v>
+        <v>1.960053</v>
       </c>
       <c r="E10" s="3" t="n">
-        <v>0.054135</v>
+        <v>1.62079</v>
       </c>
       <c r="F10" s="3" t="n">
-        <v>0.650664</v>
+        <v>1.367153</v>
       </c>
       <c r="G10" s="3" t="n">
-        <v>0.702409</v>
+        <v>2.129536</v>
       </c>
     </row>
     <row r="11">
@@ -677,19 +677,19 @@
         <v>-0.000969</v>
       </c>
       <c r="C11" s="3" t="n">
-        <v>-0.006184</v>
+        <v>-0.514823</v>
       </c>
       <c r="D11" s="3" t="n">
-        <v>-0.087992</v>
+        <v>-1.960053</v>
       </c>
       <c r="E11" s="3" t="n">
-        <v>-0.054135</v>
+        <v>-1.62079</v>
       </c>
       <c r="F11" s="3" t="n">
-        <v>-0.650664</v>
+        <v>-1.367153</v>
       </c>
       <c r="G11" s="3" t="n">
-        <v>-0.702409</v>
+        <v>-2.129536</v>
       </c>
     </row>
     <row r="12">
@@ -702,19 +702,19 @@
         <v>0</v>
       </c>
       <c r="C12" s="3" t="n">
-        <v>0</v>
+        <v>0.003495</v>
       </c>
       <c r="D12" s="3" t="n">
-        <v>0</v>
+        <v>0.012692</v>
       </c>
       <c r="E12" s="3" t="n">
-        <v>0</v>
+        <v>0.03394</v>
       </c>
       <c r="F12" s="3" t="n">
-        <v>0</v>
+        <v>0.026993</v>
       </c>
       <c r="G12" s="3" t="n">
-        <v>0</v>
+        <v>0.021053</v>
       </c>
     </row>
     <row r="13">
@@ -1109,19 +1109,19 @@
         <v>-0.021231</v>
       </c>
       <c r="C27" s="3" t="n">
-        <v>-0.6743400000000001</v>
+        <v>-0.677835</v>
       </c>
       <c r="D27" s="3" t="n">
-        <v>-2.530378</v>
+        <v>-2.54307</v>
       </c>
       <c r="E27" s="3" t="n">
-        <v>-1.664234</v>
+        <v>-1.698174</v>
       </c>
       <c r="F27" s="3" t="n">
-        <v>-1.37885</v>
+        <v>-1.405843</v>
       </c>
       <c r="G27" s="3" t="n">
-        <v>-2.154721</v>
+        <v>-2.175774</v>
       </c>
     </row>
     <row r="28">
@@ -1159,19 +1159,19 @@
         <v>-0.021231</v>
       </c>
       <c r="C29" s="3" t="n">
-        <v>-0.6743400000000001</v>
+        <v>-0.677835</v>
       </c>
       <c r="D29" s="3" t="n">
-        <v>-2.530378</v>
+        <v>-2.54307</v>
       </c>
       <c r="E29" s="3" t="n">
-        <v>-1.664234</v>
+        <v>-1.698174</v>
       </c>
       <c r="F29" s="3" t="n">
-        <v>-1.37885</v>
+        <v>-1.405843</v>
       </c>
       <c r="G29" s="3" t="n">
-        <v>-2.154721</v>
+        <v>-2.175774</v>
       </c>
     </row>
     <row r="30">
@@ -4186,7 +4186,11 @@
           <t>Reclamation deposits (note 4)</t>
         </is>
       </c>
-      <c r="D6" t="inlineStr"/>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>RestrictedCash</t>
+        </is>
+      </c>
       <c r="E6" t="inlineStr">
         <is>
           <t>-</t>
@@ -4894,7 +4898,11 @@
           <t>Reclamation deposits (note 5)</t>
         </is>
       </c>
-      <c r="D22" t="inlineStr"/>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>RestrictedCash</t>
+        </is>
+      </c>
       <c r="E22" t="inlineStr">
         <is>
           <t>-</t>
@@ -5310,7 +5318,11 @@
           <t>Reclamation deposits (note 6)</t>
         </is>
       </c>
-      <c r="D31" t="inlineStr"/>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>RestrictedCash</t>
+        </is>
+      </c>
       <c r="E31" t="inlineStr">
         <is>
           <t>-</t>
@@ -5622,7 +5634,7 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
@@ -6442,7 +6454,11 @@
           <t>Refund of reclamation deposits (note 4)</t>
         </is>
       </c>
-      <c r="D56" t="inlineStr"/>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>ChangeInRestrictedCash</t>
+        </is>
+      </c>
       <c r="E56" t="inlineStr">
         <is>
           <t>-</t>
@@ -7148,7 +7164,11 @@
           <t>Refund of reclamation deposits (note 5)</t>
         </is>
       </c>
-      <c r="D72" t="inlineStr"/>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>ChangeInRestrictedCash</t>
+        </is>
+      </c>
       <c r="E72" t="inlineStr">
         <is>
           <t>-</t>
@@ -7690,7 +7710,11 @@
           <t>Reclamation deposits (note 6)</t>
         </is>
       </c>
-      <c r="D84" t="inlineStr"/>
+      <c r="D84" t="inlineStr">
+        <is>
+          <t>ChangeInRestrictedCash</t>
+        </is>
+      </c>
       <c r="E84" t="inlineStr">
         <is>
           <t>-</t>
@@ -8334,7 +8358,7 @@
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>TotalExpenses</t>
+          <t>OperatingExpense</t>
         </is>
       </c>
       <c r="E98" t="inlineStr">
@@ -8343,19 +8367,19 @@
         </is>
       </c>
       <c r="F98" s="5" t="n">
-        <v>-0.514823</v>
+        <v>0.514823</v>
       </c>
       <c r="G98" s="5" t="n">
-        <v>-1.960053</v>
+        <v>1.960053</v>
       </c>
       <c r="H98" s="5" t="n">
-        <v>-1.62079</v>
+        <v>1.62079</v>
       </c>
       <c r="I98" s="5" t="n">
-        <v>-1.367153</v>
+        <v>1.367153</v>
       </c>
       <c r="J98" s="5" t="n">
-        <v>-2.129536</v>
+        <v>2.129536</v>
       </c>
     </row>
     <row r="99">
@@ -8376,7 +8400,7 @@
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E99" t="inlineStr">
@@ -8894,7 +8918,7 @@
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E111" t="inlineStr">
@@ -9176,7 +9200,7 @@
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E117" t="inlineStr">

--- a/output/pdf_financials_xlsx/LG.xlsx
+++ b/output/pdf_financials_xlsx/LG.xlsx
@@ -6200,7 +6200,11 @@
           <t>Deferred income tax expense (note 8)</t>
         </is>
       </c>
-      <c r="D50" t="inlineStr"/>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>DeferredTax</t>
+        </is>
+      </c>
       <c r="E50" t="inlineStr">
         <is>
           <t>-</t>
@@ -7074,7 +7078,11 @@
           <t>Deferred income tax expense (note 9)</t>
         </is>
       </c>
-      <c r="D70" t="inlineStr"/>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>DeferredTax</t>
+        </is>
+      </c>
       <c r="E70" t="inlineStr">
         <is>
           <t>-</t>
@@ -7488,7 +7496,11 @@
           <t>Deferred income tax expense (note 10)</t>
         </is>
       </c>
-      <c r="D79" t="inlineStr"/>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>DeferredTax</t>
+        </is>
+      </c>
       <c r="E79" t="inlineStr">
         <is>
           <t>-</t>
@@ -7666,7 +7678,11 @@
           <t>Deferred income tax expense</t>
         </is>
       </c>
-      <c r="D83" t="inlineStr"/>
+      <c r="D83" t="inlineStr">
+        <is>
+          <t>DeferredTax</t>
+        </is>
+      </c>
       <c r="E83" t="inlineStr">
         <is>
           <t>-</t>
